--- a/model_maker_web_v2/results/Huawei/Huawei_stage1.xlsx
+++ b/model_maker_web_v2/results/Huawei/Huawei_stage1.xlsx
@@ -521,7 +521,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SUN2000MC</t>
+          <t>Huawei</t>
         </is>
       </c>
     </row>
@@ -625,7 +625,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SUN2000MC V200R023C00 Modbus Interface Definitions.pdf</t>
+          <t>Huawei_SUN2000MC_Modbus_Interface_Definitions.pdf</t>
         </is>
       </c>
     </row>
@@ -637,7 +637,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-04-03 15:58</t>
+          <t>2026-04-03 16:03</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,11 @@
       </c>
       <c r="H21" s="11" t="inlineStr"/>
       <c r="I21" s="11" t="inlineStr"/>
-      <c r="J21" s="11" t="inlineStr"/>
+      <c r="J21" s="11" t="inlineStr">
+        <is>
+          <t>13=CEI0-21, 14=EN50438-CZ, 15=RD1699/661, 16=RD1699/661-MV48, 17=EN50438-NL, 18=C10/11... (+23)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="11" t="n">
